--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487784_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487784_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.9229</v>
+        <v>2.3244</v>
       </c>
       <c r="E2" t="n">
-        <v>3.1457</v>
+        <v>1.7527</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7772</v>
+        <v>0.5717</v>
       </c>
       <c r="G2" t="n">
         <v>1.3245</v>
@@ -610,13 +610,13 @@
         <v>1.0406</v>
       </c>
       <c r="S2" t="n">
-        <v>1.9689</v>
+        <v>0.3704</v>
       </c>
       <c r="T2" t="n">
-        <v>1.2917</v>
+        <v>-0.1014</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6773</v>
+        <v>0.4718</v>
       </c>
       <c r="V2" t="n">
         <v>2.9188</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L. GARCIA PEREZ</t>
+          <t>J. SANTOS RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,58 +643,58 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0806</v>
+        <v>0.7826</v>
       </c>
       <c r="E3" t="n">
-        <v>0.68</v>
+        <v>-0.2084</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4006</v>
+        <v>0.991</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.5249</v>
+        <v>0.1101</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3625</v>
+        <v>0.64</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.8875</v>
+        <v>-0.5299</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.1615</v>
+        <v>-0.098</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5137</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6752</v>
+        <v>-0.1747</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3634</v>
+        <v>0.2081</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1512</v>
+        <v>0.5632</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2123</v>
+        <v>-0.3551</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2081</v>
+        <v>0.8325</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2081</v>
+        <v>0.8325</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3974</v>
+        <v>-0.16</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8416</v>
+        <v>-0.1105</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5558999999999999</v>
+        <v>-0.0496</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. SANTOS RODRÍGUEZ</t>
+          <t>J. LÓPEZ YUSTE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,58 +721,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7723</v>
+        <v>0.2692</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1013</v>
+        <v>0.0611</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8735000000000001</v>
+        <v>0.2081</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1101</v>
+        <v>0.0192</v>
       </c>
       <c r="H4" t="n">
-        <v>0.64</v>
+        <v>0.0192</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5299</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.098</v>
+        <v>0.0192</v>
       </c>
       <c r="K4" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.0192</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.1747</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
         <v>0.2081</v>
       </c>
-      <c r="N4" t="n">
-        <v>0.5632</v>
-      </c>
-      <c r="O4" t="n">
-        <v>-0.3551</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.8325</v>
-      </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8325</v>
+        <v>0.2081</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1703</v>
+        <v>0.0419</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0033</v>
+        <v>0.0419</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.167</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. LÓPEZ YUSTE</t>
+          <t>L. GARCIA PEREZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,40 +799,40 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1621</v>
+        <v>0.2322</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0461</v>
+        <v>0.0371</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2081</v>
+        <v>0.1951</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0192</v>
+        <v>-0.5249</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0192</v>
+        <v>0.3625</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>-0.8875</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0192</v>
+        <v>-0.1615</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0192</v>
+        <v>0.5137</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-0.6752</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-0.3634</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-0.1512</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-0.2123</v>
       </c>
       <c r="P5" t="n">
         <v>0.2081</v>
@@ -844,13 +844,13 @@
         <v>0.2081</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.06519999999999999</v>
+        <v>0.549</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.06519999999999999</v>
+        <v>0.1986</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>0.3504</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6876</v>
+        <v>-0.2296</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.6576</v>
+        <v>-1.229</v>
       </c>
       <c r="F6" t="n">
-        <v>0.97</v>
+        <v>0.9993</v>
       </c>
       <c r="G6" t="n">
         <v>0.0477</v>
@@ -922,13 +922,13 @@
         <v>0.8325</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5271</v>
+        <v>-0.0692</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-0.1586</v>
       </c>
       <c r="U6" t="n">
-        <v>0.06</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.8047</v>
+        <v>-1.084</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.8842</v>
+        <v>-1.1341</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0795</v>
+        <v>0.0501</v>
       </c>
       <c r="G7" t="n">
         <v>-0.123</v>
@@ -1000,13 +1000,13 @@
         <v>0.8325</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.1744</v>
+        <v>-0.4243</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3876</v>
+        <v>0.3582</v>
       </c>
       <c r="V7" t="n">
         <v>0.3538</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.2153</v>
+        <v>-2.4256</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.2289</v>
+        <v>-3.586</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0135</v>
+        <v>1.1603</v>
       </c>
       <c r="G8" t="n">
         <v>-2.7324</v>
@@ -1078,13 +1078,13 @@
         <v>1.4568</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9179</v>
+        <v>-0.1282</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.2396</v>
+        <v>-0.5967</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3217</v>
+        <v>0.4685</v>
       </c>
       <c r="V8" t="n">
         <v>-0.8137</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.823</v>
+        <v>-3.1507</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.1758</v>
+        <v>-3.5329</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3528</v>
+        <v>0.3822</v>
       </c>
       <c r="G9" t="n">
         <v>-1.5881</v>
@@ -1156,13 +1156,13 @@
         <v>0.6244</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9029</v>
+        <v>-0.2306</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0439</v>
+        <v>-0.401</v>
       </c>
       <c r="U9" t="n">
-        <v>0.141</v>
+        <v>0.1703</v>
       </c>
       <c r="V9" t="n">
         <v>-0.7076</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.8993</v>
+        <v>-3.7716</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.7811</v>
+        <v>-3.8883</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1182</v>
+        <v>0.1167</v>
       </c>
       <c r="G10" t="n">
         <v>-2.2824</v>
@@ -1234,13 +1234,13 @@
         <v>0.6244</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6387</v>
+        <v>-0.511</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5905</v>
+        <v>-0.6976</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0482</v>
+        <v>0.1866</v>
       </c>
       <c r="V10" t="n">
         <v>-0.3538</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.0248</v>
+        <v>-4.0336</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.8961</v>
+        <v>-4.1104</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1287</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="G11" t="n">
         <v>-0.2363</v>
@@ -1312,13 +1312,13 @@
         <v>0.6244</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2297</v>
+        <v>-0.2385</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0619</v>
+        <v>-0.1524</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2916</v>
+        <v>-0.0861</v>
       </c>
       <c r="V11" t="n">
         <v>-1.0614</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.517</v>
+        <v>-6.9471</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.9564</v>
+        <v>-7.0636</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4395</v>
+        <v>0.1165</v>
       </c>
       <c r="G12" t="n">
         <v>-2.6896</v>
@@ -1390,13 +1390,13 @@
         <v>1.0406</v>
       </c>
       <c r="S12" t="n">
-        <v>0.67</v>
+        <v>0.2399</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.46</v>
+        <v>-0.5672</v>
       </c>
       <c r="U12" t="n">
-        <v>1.13</v>
+        <v>0.8071</v>
       </c>
       <c r="V12" t="n">
         <v>-1.1675</v>
@@ -1429,13 +1429,13 @@
         <v>-22.9018</v>
       </c>
       <c r="F13" t="n">
-        <v>4.8678</v>
+        <v>4.867800000000001</v>
       </c>
       <c r="G13" t="n">
         <v>-8.6752</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.2865000000000006</v>
+        <v>-0.2864999999999998</v>
       </c>
       <c r="I13" t="n">
         <v>-8.3888</v>
@@ -1468,13 +1468,13 @@
         <v>8.3249</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2023000000000007</v>
+        <v>-0.2023999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.968899999999999</v>
+        <v>-2.9692</v>
       </c>
       <c r="U13" t="n">
-        <v>2.7667</v>
+        <v>2.7666</v>
       </c>
       <c r="V13" t="n">
         <v>-0.8313999999999999</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. JANKOVIC</t>
+          <t>N. DEDOVIC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.2707</v>
+        <v>6.2695</v>
       </c>
       <c r="E14" t="n">
-        <v>1.2064</v>
+        <v>4.3736</v>
       </c>
       <c r="F14" t="n">
-        <v>4.0642</v>
+        <v>1.8959</v>
       </c>
       <c r="G14" t="n">
-        <v>5.5624</v>
+        <v>4.7364</v>
       </c>
       <c r="H14" t="n">
-        <v>5.3665</v>
+        <v>4.0383</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1959</v>
+        <v>0.698</v>
       </c>
       <c r="J14" t="n">
-        <v>4.5584</v>
+        <v>4.2794</v>
       </c>
       <c r="K14" t="n">
-        <v>4.6155</v>
+        <v>3.6222</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.0572</v>
+        <v>0.6572</v>
       </c>
       <c r="M14" t="n">
-        <v>1.004</v>
+        <v>0.457</v>
       </c>
       <c r="N14" t="n">
-        <v>0.7509</v>
+        <v>0.4162</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2531</v>
+        <v>0.0408</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.8325</v>
+        <v>2.0812</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.1218</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.2893</v>
+        <v>2.0812</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.043</v>
+        <v>0.0357</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.0439</v>
+        <v>-0.4895</v>
       </c>
       <c r="U14" t="n">
-        <v>1.0009</v>
+        <v>0.5252</v>
       </c>
       <c r="V14" t="n">
+        <v>-0.5838</v>
+      </c>
+      <c r="W14" t="n">
         <v>0.5838</v>
       </c>
-      <c r="W14" t="n">
-        <v>0.8137</v>
-      </c>
       <c r="X14" t="n">
-        <v>-0.23</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>N. DEDOVIC</t>
+          <t>M. JANKOVIC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.1671</v>
+        <v>5.7184</v>
       </c>
       <c r="E15" t="n">
-        <v>3.6235</v>
+        <v>1.7422</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5436</v>
+        <v>3.9762</v>
       </c>
       <c r="G15" t="n">
-        <v>4.7364</v>
+        <v>5.5624</v>
       </c>
       <c r="H15" t="n">
-        <v>4.0383</v>
+        <v>5.3665</v>
       </c>
       <c r="I15" t="n">
-        <v>0.698</v>
+        <v>0.1959</v>
       </c>
       <c r="J15" t="n">
-        <v>4.2794</v>
+        <v>4.5584</v>
       </c>
       <c r="K15" t="n">
-        <v>3.6222</v>
+        <v>4.6155</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6572</v>
+        <v>-0.0572</v>
       </c>
       <c r="M15" t="n">
-        <v>0.457</v>
+        <v>1.004</v>
       </c>
       <c r="N15" t="n">
-        <v>0.4162</v>
+        <v>0.7509</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0408</v>
+        <v>0.2531</v>
       </c>
       <c r="P15" t="n">
-        <v>2.0812</v>
+        <v>-0.8325</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-3.1218</v>
       </c>
       <c r="R15" t="n">
-        <v>2.0812</v>
+        <v>2.2893</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0667</v>
+        <v>0.4047</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.2396</v>
+        <v>-0.5081</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1729</v>
+        <v>0.9127999999999999</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.5838</v>
+        <v>0.5838</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5838</v>
+        <v>0.8137</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.1675</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. LATORRE SANCHEZ</t>
+          <t>J. CEBOLLA HERRERA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.191</v>
+        <v>2.5704</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8105</v>
+        <v>-1.0324</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3806</v>
+        <v>3.6028</v>
       </c>
       <c r="G16" t="n">
-        <v>1.3156</v>
+        <v>-0.8647</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.2432</v>
+        <v>-1.8167</v>
       </c>
       <c r="I16" t="n">
-        <v>3.5588</v>
+        <v>0.9519</v>
       </c>
       <c r="J16" t="n">
-        <v>1.0095</v>
+        <v>-1.9994</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.0472</v>
+        <v>-1.9512</v>
       </c>
       <c r="L16" t="n">
-        <v>3.0567</v>
+        <v>-0.0482</v>
       </c>
       <c r="M16" t="n">
-        <v>0.3061</v>
+        <v>1.1347</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.196</v>
+        <v>0.1346</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5021</v>
+        <v>1.0001</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.2081</v>
+        <v>2.2893</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.8325</v>
+        <v>2.2893</v>
       </c>
       <c r="S16" t="n">
-        <v>1.8359</v>
+        <v>-0.0217</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8416</v>
+        <v>-0.2005</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9943</v>
+        <v>0.1788</v>
       </c>
       <c r="V16" t="n">
-        <v>0.2477</v>
+        <v>1.1675</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X16" t="n">
-        <v>0.2477</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. DIBBA</t>
+          <t>A. LATORRE SANCHEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.1699</v>
+        <v>1.8538</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.6545</v>
+        <v>0.0604</v>
       </c>
       <c r="F17" t="n">
-        <v>4.8244</v>
+        <v>1.7934</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.8205</v>
+        <v>1.3156</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.1154</v>
+        <v>-2.2432</v>
       </c>
       <c r="I17" t="n">
-        <v>1.2949</v>
+        <v>3.5588</v>
       </c>
       <c r="J17" t="n">
-        <v>-2.0736</v>
+        <v>1.0095</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.1519</v>
+        <v>-2.0472</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0784</v>
+        <v>3.0567</v>
       </c>
       <c r="M17" t="n">
-        <v>1.253</v>
+        <v>0.3061</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0366</v>
+        <v>-0.196</v>
       </c>
       <c r="O17" t="n">
-        <v>1.2165</v>
+        <v>0.5021</v>
       </c>
       <c r="P17" t="n">
-        <v>1.4568</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R17" t="n">
-        <v>2.4974</v>
+        <v>0.8325</v>
       </c>
       <c r="S17" t="n">
-        <v>2.3037</v>
+        <v>0.4986</v>
       </c>
       <c r="T17" t="n">
-        <v>1.2297</v>
+        <v>0.0915</v>
       </c>
       <c r="U17" t="n">
-        <v>1.074</v>
+        <v>0.4071</v>
       </c>
       <c r="V17" t="n">
-        <v>0.23</v>
+        <v>0.2477</v>
       </c>
       <c r="W17" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.2477</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. CEBOLLA HERRERA</t>
+          <t>R. SANTOS JIMENEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.1902</v>
+        <v>1.724</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.3538</v>
+        <v>-1.0948</v>
       </c>
       <c r="F18" t="n">
-        <v>3.5441</v>
+        <v>2.8188</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.8647</v>
+        <v>0.6656</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.8167</v>
+        <v>0.5668</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9519</v>
+        <v>0.0988</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.9994</v>
+        <v>0.2412</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.9512</v>
+        <v>0.2894</v>
       </c>
       <c r="L18" t="n">
         <v>-0.0482</v>
       </c>
       <c r="M18" t="n">
-        <v>1.1347</v>
+        <v>0.4244</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1346</v>
+        <v>0.2775</v>
       </c>
       <c r="O18" t="n">
-        <v>1.0001</v>
+        <v>0.147</v>
       </c>
       <c r="P18" t="n">
-        <v>2.2893</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.0812</v>
       </c>
       <c r="R18" t="n">
-        <v>2.2893</v>
+        <v>2.0812</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4019</v>
+        <v>0.2447</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5219</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1201</v>
+        <v>0.3132</v>
       </c>
       <c r="V18" t="n">
-        <v>1.1675</v>
+        <v>0.8137</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1675</v>
+        <v>0.8137</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. SANTOS JIMENEZ</t>
+          <t>S. CECILIA PEREZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.6947</v>
+        <v>1.5898</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0948</v>
+        <v>0.3389</v>
       </c>
       <c r="F19" t="n">
-        <v>2.7895</v>
+        <v>1.2508</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6656</v>
+        <v>1.2474</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5668</v>
+        <v>-0.0041</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0988</v>
+        <v>1.2516</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2412</v>
+        <v>0.8842</v>
       </c>
       <c r="K19" t="n">
-        <v>0.2894</v>
+        <v>0.3838</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.0482</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4244</v>
+        <v>0.3632</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2775</v>
+        <v>-0.3879</v>
       </c>
       <c r="O19" t="n">
-        <v>0.147</v>
+        <v>0.7511</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.2487</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.0812</v>
+        <v>1.2487</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2153</v>
+        <v>-0.6764</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.5453</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2838</v>
+        <v>-0.1311</v>
       </c>
       <c r="V19" t="n">
-        <v>0.8137</v>
+        <v>-0.23</v>
       </c>
       <c r="W19" t="n">
-        <v>0.8137</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. CECILIA PEREZ</t>
+          <t>L. DIBBA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.2184</v>
+        <v>1.4628</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2318</v>
+        <v>-2.8332</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9866</v>
+        <v>4.2959</v>
       </c>
       <c r="G20" t="n">
-        <v>1.2474</v>
+        <v>-0.8205</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0041</v>
+        <v>-2.1154</v>
       </c>
       <c r="I20" t="n">
-        <v>1.2516</v>
+        <v>1.2949</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8842</v>
+        <v>-2.0736</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3838</v>
+        <v>-2.1519</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5004999999999999</v>
+        <v>0.0784</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3632</v>
+        <v>1.253</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3879</v>
+        <v>0.0366</v>
       </c>
       <c r="O20" t="n">
-        <v>0.7511</v>
+        <v>1.2165</v>
       </c>
       <c r="P20" t="n">
-        <v>1.2487</v>
+        <v>1.4568</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2487</v>
+        <v>2.4974</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0478</v>
+        <v>0.5965</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6524</v>
+        <v>0.051</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3953</v>
+        <v>0.5455</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.23</v>
+        <v>0.23</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0425</v>
+        <v>0.3567</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.432</v>
+        <v>-2.0034</v>
       </c>
       <c r="F21" t="n">
-        <v>2.3894</v>
+        <v>2.3601</v>
       </c>
       <c r="G21" t="n">
         <v>-1.2373</v>
@@ -2092,13 +2092,13 @@
         <v>1.6649</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.824</v>
+        <v>-0.4247</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.1091</v>
+        <v>-0.6805</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2852</v>
+        <v>0.2558</v>
       </c>
       <c r="V21" t="n">
         <v>0.3538</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1723</v>
+        <v>-0.1429</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1723</v>
+        <v>-0.1429</v>
       </c>
       <c r="G22" t="n">
         <v>-0.049</v>
@@ -2170,13 +2170,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1233</v>
+        <v>-0.0939</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1233</v>
+        <v>-0.0939</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.8095</v>
+        <v>-1.1167</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.2095</v>
+        <v>-1.7809</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4</v>
+        <v>0.6643</v>
       </c>
       <c r="G23" t="n">
         <v>0.8344</v>
@@ -2248,13 +2248,13 @@
         <v>0.4162</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.852</v>
+        <v>-0.1592</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7829</v>
+        <v>-0.3543</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.06909999999999999</v>
+        <v>0.1951</v>
       </c>
       <c r="V23" t="n">
         <v>-1.1675</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.8439</v>
+        <v>-2.252</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.9955</v>
+        <v>-2.6384</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1515</v>
+        <v>0.3864</v>
       </c>
       <c r="G24" t="n">
         <v>-2.715</v>
@@ -2326,13 +2326,13 @@
         <v>1.2487</v>
       </c>
       <c r="S24" t="n">
-        <v>0.2061</v>
+        <v>-0.2019</v>
       </c>
       <c r="T24" t="n">
-        <v>0.5806</v>
+        <v>-0.0624</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3744</v>
+        <v>-0.1396</v>
       </c>
       <c r="V24" t="n">
         <v>-0.5838</v>
@@ -2362,25 +2362,25 @@
         <v>18.0338</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.8679</v>
+        <v>-4.868</v>
       </c>
       <c r="F25" t="n">
-        <v>22.90159999999999</v>
+        <v>22.9017</v>
       </c>
       <c r="G25" t="n">
         <v>8.675300000000002</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2864999999999993</v>
+        <v>0.2864999999999998</v>
       </c>
       <c r="I25" t="n">
         <v>8.3888</v>
       </c>
       <c r="J25" t="n">
-        <v>2.6148</v>
+        <v>2.614799999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>0.8596000000000004</v>
+        <v>0.8595999999999999</v>
       </c>
       <c r="L25" t="n">
         <v>1.7552</v>
@@ -2389,10 +2389,10 @@
         <v>6.0604</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.5728999999999999</v>
+        <v>-0.5729</v>
       </c>
       <c r="O25" t="n">
-        <v>6.633499999999999</v>
+        <v>6.633500000000001</v>
       </c>
       <c r="P25" t="n">
         <v>8.3246</v>
@@ -2404,13 +2404,13 @@
         <v>16.6494</v>
       </c>
       <c r="S25" t="n">
-        <v>0.2022999999999999</v>
+        <v>0.2024</v>
       </c>
       <c r="T25" t="n">
-        <v>-2.7664</v>
+        <v>-2.7666</v>
       </c>
       <c r="U25" t="n">
-        <v>2.9691</v>
+        <v>2.9689</v>
       </c>
       <c r="V25" t="n">
         <v>0.8314</v>
